--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -21809,7 +21809,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E9689B9B-B69C-4523-828A-2AF72A67449E}</x14:id>
+          <x14:id>{BC5D7B14-44BF-43FC-836A-84403DF54B81}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21940,7 +21940,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E9689B9B-B69C-4523-828A-2AF72A67449E}">
+          <x14:cfRule type="dataBar" id="{BC5D7B14-44BF-43FC-836A-84403DF54B81}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
